--- a/grupos/5ARHV - Estadisticos 20241.xlsx
+++ b/grupos/5ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -164,21 +164,21 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
+    <t>Morales Estrada Adilene</t>
+  </si>
+  <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
   </si>
   <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
-    <t>Morales Estrada Adilene</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,7 +191,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CHONKOA</t>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -203,10 +203,7 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>VALLEJO</t>
@@ -218,10 +215,7 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
+    <t>EMILIANO GERARDO</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
@@ -231,9 +225,6 @@
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>CRISTIAN LEOBARDO</t>
   </si>
 </sst>
 </file>
@@ -741,22 +732,22 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -777,10 +768,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -789,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -818,22 +809,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -857,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -895,22 +886,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -937,7 +928,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -972,22 +963,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1008,22 +999,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
+        <v>7</v>
+      </c>
+      <c r="U7">
+        <v>8</v>
+      </c>
+      <c r="V7">
+        <v>8</v>
+      </c>
+      <c r="W7">
+        <v>7</v>
+      </c>
+      <c r="X7">
         <v>6</v>
       </c>
-      <c r="U7">
-        <v>7</v>
-      </c>
-      <c r="V7">
-        <v>7</v>
-      </c>
-      <c r="W7">
-        <v>5</v>
-      </c>
-      <c r="X7">
-        <v>5</v>
-      </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1049,22 +1040,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1088,16 +1079,16 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>5</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1126,22 +1117,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1162,19 +1153,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1203,22 +1194,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1239,16 +1230,16 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1280,22 +1271,22 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1316,10 +1307,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1357,22 +1348,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1393,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1434,22 +1425,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1470,16 +1461,16 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1511,22 +1502,22 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1547,22 +1538,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>9</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1588,22 +1579,22 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1624,13 +1615,13 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1665,22 +1656,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1701,19 +1692,19 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>8</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1742,22 +1733,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1778,10 +1769,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1822,19 +1813,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1870,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1896,22 +1887,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1932,13 +1923,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>7</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -1973,22 +1964,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2009,13 +2000,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2050,22 +2041,22 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2086,13 +2077,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2127,22 +2118,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2163,10 +2154,10 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2175,7 +2166,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2204,22 +2195,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2240,22 +2231,22 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2281,22 +2272,22 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2323,13 +2314,13 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2358,22 +2349,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2400,13 +2391,13 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2435,22 +2426,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2474,13 +2465,13 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2622,40 +2613,40 @@
         <v>93.3</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J4">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="K4">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P4">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q4">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>93.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2681,7 +2672,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2699,7 +2690,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2740,7 +2731,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -2758,7 +2749,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2799,40 +2790,40 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J7">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N7">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2858,7 +2849,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -2870,13 +2861,13 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2888,7 +2879,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -2917,40 +2908,40 @@
         <v>96.7</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="I9">
         <v>100</v>
       </c>
       <c r="J9">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M9">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="N9">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="Q9">
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2976,7 +2967,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -2994,7 +2985,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3035,10 +3026,10 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -3047,16 +3038,16 @@
         <v>81.3</v>
       </c>
       <c r="L11">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -3065,10 +3056,10 @@
         <v>81.3</v>
       </c>
       <c r="R11">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3094,7 +3085,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -3106,13 +3097,13 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3124,7 +3115,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3153,7 +3144,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -3171,7 +3162,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3215,7 +3206,7 @@
         <v>95</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3224,16 +3215,16 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="M14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="N14">
         <v>95</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3242,10 +3233,10 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>93.3</v>
+        <v>95</v>
       </c>
       <c r="S14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3271,7 +3262,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -3289,7 +3280,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3330,10 +3321,10 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3348,10 +3339,10 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -3398,10 +3389,10 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M17">
         <v>96.7</v>
@@ -3416,10 +3407,10 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S17">
         <v>96.7</v>
@@ -3448,10 +3439,10 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -3460,16 +3451,16 @@
         <v>100</v>
       </c>
       <c r="L18">
+        <v>93.3</v>
+      </c>
+      <c r="M18">
         <v>96.7</v>
       </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
-        <v>95</v>
+        <v>47.5</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -3478,10 +3469,10 @@
         <v>100</v>
       </c>
       <c r="R18">
+        <v>93.3</v>
+      </c>
+      <c r="S18">
         <v>96.7</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3507,7 +3498,7 @@
         <v>96.7</v>
       </c>
       <c r="H19">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -3519,13 +3510,13 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="M19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -3537,10 +3528,10 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="S19">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3566,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -3578,13 +3569,13 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3596,7 +3587,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3625,10 +3616,10 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -3643,10 +3634,10 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3687,7 +3678,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22">
         <v>100</v>
@@ -3705,7 +3696,7 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -3743,10 +3734,10 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -3755,16 +3746,16 @@
         <v>81.3</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O23">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -3773,7 +3764,7 @@
         <v>81.3</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -3876,7 +3867,7 @@
         <v>96.7</v>
       </c>
       <c r="M25">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="N25">
         <v>95</v>
@@ -3894,7 +3885,7 @@
         <v>96.7</v>
       </c>
       <c r="S25">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3923,7 +3914,7 @@
         <v>95</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -3932,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M26">
         <v>96.7</v>
@@ -3941,7 +3932,7 @@
         <v>95</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -3950,7 +3941,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S26">
         <v>96.7</v>
@@ -4019,19 +4010,19 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>73.90000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>26.1</v>
+        <v>17.4</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4042,7 +4033,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
@@ -4063,7 +4054,7 @@
         <v>4.3</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4074,7 +4065,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4083,19 +4074,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4106,7 +4097,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -4115,19 +4106,19 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4138,7 +4129,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>51</v>
@@ -4159,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4170,7 +4161,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
@@ -4191,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4241,7 +4232,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4273,16 +4264,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920393</v>
+        <v>22330051920205</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -4296,22 +4287,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920393</v>
+        <v>22330051920205</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4325,10 +4316,10 @@
         <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -4348,10 +4339,10 @@
         <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4371,10 +4362,10 @@
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4383,29 +4374,6 @@
         <v>47</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920229</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20241.xlsx
+++ b/grupos/5ARHV - Estadisticos 20241.xlsx
@@ -1810,7 +1810,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -3439,7 +3439,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>47.5</v>
+        <v>92.5</v>
       </c>
       <c r="I18">
         <v>98</v>
@@ -3457,7 +3457,7 @@
         <v>96.7</v>
       </c>
       <c r="N18">
-        <v>47.5</v>
+        <v>92.5</v>
       </c>
       <c r="O18">
         <v>98</v>

--- a/grupos/5ARHV - Estadisticos 20241.xlsx
+++ b/grupos/5ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -116,6 +116,9 @@
     <t>SILVESTRE OLIVARES MICHELLE</t>
   </si>
   <si>
+    <t>TIBURCIO ORTEGA ANGELA</t>
+  </si>
+  <si>
     <t>TRUJILLO ------ AMERICA</t>
   </si>
   <si>
@@ -164,18 +167,18 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Morales Estrada Adilene</t>
+  </si>
+  <si>
+    <t>Hernandez Alonso Antonio Ascari</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Morales Estrada Adilene</t>
-  </si>
-  <si>
-    <t>Hernandez Alonso Antonio Ascari</t>
-  </si>
-  <si>
     <t>Martínez López Miguel Ángel</t>
   </si>
   <si>
@@ -189,6 +192,15 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
   </si>
   <si>
     <t>ANTONIO</t>
@@ -586,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -753,10 +765,10 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -765,13 +777,13 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>6</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -783,7 +795,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -830,10 +842,10 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -842,7 +854,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -907,10 +919,10 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -919,7 +931,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -984,10 +996,10 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -996,7 +1008,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1061,10 +1073,10 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1073,16 +1085,16 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1138,10 +1150,10 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1150,7 +1162,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1215,10 +1227,10 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1227,7 +1239,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1292,10 +1304,10 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1304,7 +1316,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1369,10 +1381,10 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1381,7 +1393,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1446,10 +1458,10 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1458,7 +1470,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>7</v>
@@ -1523,10 +1535,10 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1535,7 +1547,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1600,10 +1612,10 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1612,7 +1624,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1677,10 +1689,10 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1689,7 +1701,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1754,10 +1766,10 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1766,16 +1778,16 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1831,10 +1843,10 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1843,7 +1855,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1852,7 +1864,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -1908,10 +1920,10 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -1920,13 +1932,13 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -1985,10 +1997,10 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -1997,7 +2009,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>8</v>
@@ -2006,7 +2018,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2062,10 +2074,10 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2074,7 +2086,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2139,10 +2151,10 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2151,7 +2163,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2216,10 +2228,10 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2228,13 +2240,13 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2254,40 +2266,40 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="C24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="D24">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="H24">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="M24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2299,7 +2311,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2308,22 +2320,22 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2346,34 +2358,34 @@
         <v>9</v>
       </c>
       <c r="G25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <v>9</v>
       </c>
       <c r="I25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <v>10</v>
       </c>
       <c r="K25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>10</v>
       </c>
       <c r="M25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2382,7 +2394,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2394,13 +2406,13 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2411,72 +2423,149 @@
         <v>9</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>9</v>
+      </c>
+      <c r="H26">
+        <v>9</v>
+      </c>
+      <c r="I26">
+        <v>9</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26">
+        <v>10</v>
+      </c>
+      <c r="L26">
+        <v>10</v>
+      </c>
+      <c r="M26">
+        <v>9</v>
+      </c>
+      <c r="N26">
+        <v>-1</v>
+      </c>
+      <c r="O26">
+        <v>10</v>
+      </c>
+      <c r="P26">
+        <v>10</v>
+      </c>
+      <c r="Q26">
+        <v>-1</v>
+      </c>
+      <c r="R26">
+        <v>-1</v>
+      </c>
+      <c r="S26">
+        <v>10</v>
+      </c>
+      <c r="T26">
+        <v>9</v>
+      </c>
+      <c r="U26">
+        <v>10</v>
+      </c>
+      <c r="V26">
+        <v>10</v>
+      </c>
+      <c r="W26">
+        <v>10</v>
+      </c>
+      <c r="X26">
+        <v>10</v>
+      </c>
+      <c r="Y26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>8</v>
+      </c>
+      <c r="E27">
         <v>5</v>
       </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="G26">
-        <v>8</v>
-      </c>
-      <c r="H26">
-        <v>9</v>
-      </c>
-      <c r="I26">
-        <v>8</v>
-      </c>
-      <c r="J26">
-        <v>8</v>
-      </c>
-      <c r="K26">
-        <v>7</v>
-      </c>
-      <c r="L26">
-        <v>8</v>
-      </c>
-      <c r="M26">
-        <v>8</v>
-      </c>
-      <c r="N26">
-        <v>-1</v>
-      </c>
-      <c r="O26">
-        <v>-1</v>
-      </c>
-      <c r="P26">
-        <v>-1</v>
-      </c>
-      <c r="Q26">
-        <v>-1</v>
-      </c>
-      <c r="R26">
-        <v>-1</v>
-      </c>
-      <c r="S26">
-        <v>-1</v>
-      </c>
-      <c r="T26">
-        <v>9</v>
-      </c>
-      <c r="U26">
-        <v>8</v>
-      </c>
-      <c r="V26">
-        <v>8</v>
-      </c>
-      <c r="W26">
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>9</v>
+      </c>
+      <c r="I27">
+        <v>8</v>
+      </c>
+      <c r="J27">
+        <v>8</v>
+      </c>
+      <c r="K27">
+        <v>7</v>
+      </c>
+      <c r="L27">
+        <v>8</v>
+      </c>
+      <c r="M27">
+        <v>8</v>
+      </c>
+      <c r="N27">
+        <v>-1</v>
+      </c>
+      <c r="O27">
+        <v>7</v>
+      </c>
+      <c r="P27">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>-1</v>
+      </c>
+      <c r="R27">
+        <v>-1</v>
+      </c>
+      <c r="S27">
+        <v>8</v>
+      </c>
+      <c r="T27">
+        <v>9</v>
+      </c>
+      <c r="U27">
+        <v>7</v>
+      </c>
+      <c r="V27">
+        <v>8</v>
+      </c>
+      <c r="W27">
         <v>6</v>
       </c>
-      <c r="X26">
-        <v>8</v>
-      </c>
-      <c r="Y26">
+      <c r="X27">
+        <v>8</v>
+      </c>
+      <c r="Y27">
         <v>8</v>
       </c>
     </row>
@@ -2493,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2502,7 +2591,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2510,7 +2599,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -2518,7 +2607,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -2634,19 +2723,19 @@
         <v>92.5</v>
       </c>
       <c r="O4">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P4">
-        <v>97.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>90.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2699,7 +2788,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -2758,7 +2847,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -2811,19 +2900,19 @@
         <v>92.5</v>
       </c>
       <c r="O7">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="P7">
-        <v>97.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R7">
         <v>98.3</v>
       </c>
       <c r="S7">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2876,7 +2965,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R8">
         <v>98.3</v>
@@ -2929,19 +3018,19 @@
         <v>87.5</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P9">
-        <v>97.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R9">
         <v>95</v>
       </c>
       <c r="S9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2994,7 +3083,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3047,19 +3136,19 @@
         <v>87.5</v>
       </c>
       <c r="O11">
-        <v>92</v>
+        <v>91.3</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>81.3</v>
+        <v>54.2</v>
       </c>
       <c r="R11">
         <v>88.3</v>
       </c>
       <c r="S11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3112,7 +3201,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R12">
         <v>96.7</v>
@@ -3165,13 +3254,13 @@
         <v>97.5</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3224,19 +3313,19 @@
         <v>95</v>
       </c>
       <c r="O14">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R14">
         <v>95</v>
       </c>
       <c r="S14">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3289,7 +3378,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3342,13 +3431,13 @@
         <v>97.5</v>
       </c>
       <c r="O16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3401,19 +3490,19 @@
         <v>95</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>90.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="R17">
         <v>95</v>
       </c>
       <c r="S17">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3460,19 +3549,19 @@
         <v>92.5</v>
       </c>
       <c r="O18">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R18">
         <v>93.3</v>
       </c>
       <c r="S18">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3519,19 +3608,19 @@
         <v>92.5</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R19">
         <v>98.3</v>
       </c>
       <c r="S19">
-        <v>98.3</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3584,7 +3673,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R20">
         <v>95</v>
@@ -3637,13 +3726,13 @@
         <v>97.5</v>
       </c>
       <c r="O21">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3696,13 +3785,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R22">
         <v>96.7</v>
@@ -3755,13 +3844,13 @@
         <v>80</v>
       </c>
       <c r="O23">
-        <v>92</v>
+        <v>93.8</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>81.3</v>
+        <v>54.2</v>
       </c>
       <c r="R23">
         <v>93.3</v>
@@ -3775,58 +3864,58 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3834,7 +3923,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -3846,13 +3935,13 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -3864,13 +3953,13 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -3879,13 +3968,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="R25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>98.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -3905,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="G26">
         <v>96.7</v>
@@ -3914,7 +4003,7 @@
         <v>95</v>
       </c>
       <c r="I26">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -3923,28 +4012,87 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="M26">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="N26">
         <v>95</v>
       </c>
       <c r="O26">
+        <v>100</v>
+      </c>
+      <c r="P26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>66.7</v>
+      </c>
+      <c r="R26">
+        <v>96.7</v>
+      </c>
+      <c r="S26">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27">
+        <v>95</v>
+      </c>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>100</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
+        <v>96.7</v>
+      </c>
+      <c r="H27">
+        <v>95</v>
+      </c>
+      <c r="I27">
         <v>98</v>
       </c>
-      <c r="P26">
-        <v>100</v>
-      </c>
-      <c r="Q26">
-        <v>100</v>
-      </c>
-      <c r="R26">
+      <c r="J27">
+        <v>100</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
         <v>95</v>
       </c>
-      <c r="S26">
+      <c r="M27">
         <v>96.7</v>
+      </c>
+      <c r="N27">
+        <v>95</v>
+      </c>
+      <c r="O27">
+        <v>95</v>
+      </c>
+      <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>66.7</v>
+      </c>
+      <c r="R27">
+        <v>95</v>
+      </c>
+      <c r="S27">
+        <v>97.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3972,31 +4120,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4004,22 +4152,22 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="G2" s="2">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="H2">
         <v>7.5</v>
@@ -4033,45 +4181,45 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3">
+        <v>24</v>
+      </c>
+      <c r="D3">
         <v>23</v>
       </c>
-      <c r="D3">
-        <v>22</v>
-      </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>95.8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
-        <v>95.7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>4.3</v>
-      </c>
-      <c r="H3">
-        <v>8.9</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>23</v>
@@ -4080,30 +4228,30 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>23</v>
@@ -4112,30 +4260,30 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>23</v>
@@ -4144,19 +4292,19 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4164,10 +4312,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>23</v>
@@ -4176,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -4185,10 +4333,10 @@
         <v>8.9</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
@@ -4198,7 +4346,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4207,22 +4355,122 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920225</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920225</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920225</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920225</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4232,7 +4480,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4241,22 +4489,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4267,19 +4515,19 @@
         <v>22330051920205</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4287,19 +4535,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920205</v>
+        <v>22330051920394</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>48</v>
@@ -4310,22 +4558,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920394</v>
+        <v>22330051920374</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4333,47 +4581,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920374</v>
+        <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920222</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20241.xlsx
+++ b/grupos/5ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -762,7 +762,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>7</v>
@@ -774,13 +774,13 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>8</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -839,7 +839,7 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -851,7 +851,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -928,7 +928,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -993,7 +993,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1005,7 +1005,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1070,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1159,7 +1159,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1224,7 +1224,7 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1236,13 +1236,13 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>10</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1301,7 +1301,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1313,7 +1313,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1378,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -1390,13 +1390,13 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1455,7 +1455,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>9</v>
@@ -1467,7 +1467,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1485,7 +1485,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1532,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1544,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1609,7 +1609,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1621,13 +1621,13 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1686,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1698,13 +1698,13 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>10</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>9</v>
@@ -1775,13 +1775,13 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1840,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -1852,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
@@ -1917,7 +1917,7 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -1929,13 +1929,13 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>8</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -1994,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2006,7 +2006,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>8</v>
@@ -2071,7 +2071,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2083,13 +2083,13 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>9</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2148,7 +2148,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2160,13 +2160,13 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>10</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2225,7 +2225,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>9</v>
@@ -2237,7 +2237,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2278,7 +2278,7 @@
         <v>8</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -2296,7 +2296,7 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2314,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>10</v>
@@ -2391,7 +2391,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2456,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2468,7 +2468,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2486,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2533,7 +2533,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -2545,7 +2545,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>8</v>
@@ -2720,7 +2720,7 @@
         <v>95</v>
       </c>
       <c r="N4">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="O4">
         <v>95</v>
@@ -2779,7 +2779,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2838,7 +2838,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2897,7 +2897,7 @@
         <v>98.3</v>
       </c>
       <c r="N7">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O7">
         <v>96.3</v>
@@ -2909,7 +2909,7 @@
         <v>66.7</v>
       </c>
       <c r="R7">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S7">
         <v>99</v>
@@ -2968,7 +2968,7 @@
         <v>66.7</v>
       </c>
       <c r="R8">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3015,7 +3015,7 @@
         <v>95</v>
       </c>
       <c r="N9">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="O9">
         <v>98.8</v>
@@ -3027,7 +3027,7 @@
         <v>66.7</v>
       </c>
       <c r="R9">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="S9">
         <v>96.90000000000001</v>
@@ -3074,7 +3074,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3133,7 +3133,7 @@
         <v>96.7</v>
       </c>
       <c r="N11">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O11">
         <v>91.3</v>
@@ -3145,7 +3145,7 @@
         <v>54.2</v>
       </c>
       <c r="R11">
-        <v>88.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S11">
         <v>97.90000000000001</v>
@@ -3192,7 +3192,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3204,7 +3204,7 @@
         <v>66.7</v>
       </c>
       <c r="R12">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3251,7 +3251,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="O13">
         <v>96.3</v>
@@ -3263,7 +3263,7 @@
         <v>66.7</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3310,7 +3310,7 @@
         <v>96.7</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O14">
         <v>97.5</v>
@@ -3322,7 +3322,7 @@
         <v>66.7</v>
       </c>
       <c r="R14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S14">
         <v>97.90000000000001</v>
@@ -3369,7 +3369,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3428,7 +3428,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O16">
         <v>98.8</v>
@@ -3487,7 +3487,7 @@
         <v>96.7</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="O17">
         <v>97.5</v>
@@ -3499,7 +3499,7 @@
         <v>60.4</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>95.8</v>
       </c>
       <c r="S17">
         <v>97.90000000000001</v>
@@ -3546,7 +3546,7 @@
         <v>96.7</v>
       </c>
       <c r="N18">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O18">
         <v>97.5</v>
@@ -3558,7 +3558,7 @@
         <v>66.7</v>
       </c>
       <c r="R18">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="S18">
         <v>97.90000000000001</v>
@@ -3605,7 +3605,7 @@
         <v>98.3</v>
       </c>
       <c r="N19">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O19">
         <v>98.8</v>
@@ -3617,7 +3617,7 @@
         <v>66.7</v>
       </c>
       <c r="R19">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="S19">
         <v>99</v>
@@ -3664,7 +3664,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3676,7 +3676,7 @@
         <v>66.7</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3723,7 +3723,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O21">
         <v>96.3</v>
@@ -3794,7 +3794,7 @@
         <v>66.7</v>
       </c>
       <c r="R22">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -3841,7 +3841,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="O23">
         <v>93.8</v>
@@ -3853,7 +3853,7 @@
         <v>54.2</v>
       </c>
       <c r="R23">
-        <v>93.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -3876,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>0</v>
@@ -3912,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>98.3</v>
       </c>
       <c r="N26">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4030,7 +4030,7 @@
         <v>66.7</v>
       </c>
       <c r="R26">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S26">
         <v>99</v>
@@ -4077,7 +4077,7 @@
         <v>96.7</v>
       </c>
       <c r="N27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O27">
         <v>95</v>
@@ -4089,7 +4089,7 @@
         <v>66.7</v>
       </c>
       <c r="R27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S27">
         <v>97.90000000000001</v>
@@ -4202,7 +4202,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4318,25 +4318,25 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4346,7 +4346,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4453,26 +4453,6 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920225</v>
-      </c>
-      <c r="B6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4480,7 +4460,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4512,93 +4492,185 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920205</v>
+        <v>22330051920225</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920394</v>
+        <v>22330051920225</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920374</v>
+        <v>22330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
+        <v>22330051920225</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920394</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920374</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
         <v>22330051920222</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>64</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C9" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D9" t="s">
         <v>72</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>48</v>
       </c>
-      <c r="G5">
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ARHV - Estadisticos 20241.xlsx
+++ b/grupos/5ARHV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="58">
   <si>
     <t>Materia</t>
   </si>
@@ -192,51 +192,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>KARLA YARITZY</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
   </si>
 </sst>
 </file>
@@ -771,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -789,7 +744,7 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -848,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -925,7 +880,7 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1002,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1079,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1097,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1156,7 +1111,7 @@
         <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>8</v>
@@ -1233,7 +1188,7 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
@@ -1310,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>8</v>
@@ -1328,7 +1283,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1387,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1464,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>6</v>
@@ -1541,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>9</v>
@@ -1618,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1695,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>9</v>
@@ -1772,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -1790,7 +1745,7 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1849,7 +1804,7 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -1926,7 +1881,7 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -1944,7 +1899,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2003,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>9</v>
@@ -2021,7 +1976,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2080,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>8</v>
@@ -2157,7 +2112,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>9</v>
@@ -2234,7 +2189,7 @@
         <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2266,13 +2221,13 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2281,16 +2236,16 @@
         <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>8</v>
@@ -2299,16 +2254,16 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2317,16 +2272,16 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2335,7 +2290,7 @@
         <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2388,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2465,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2542,7 +2497,7 @@
         <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>8</v>
@@ -2560,7 +2515,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2729,7 +2684,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q4">
-        <v>60.4</v>
+        <v>93.8</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -2788,7 +2743,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -2847,7 +2802,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -2906,7 +2861,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R7">
         <v>99</v>
@@ -2965,7 +2920,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>99</v>
@@ -3024,7 +2979,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="Q9">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R9">
         <v>94.8</v>
@@ -3083,7 +3038,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3142,7 +3097,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>54.2</v>
+        <v>87.5</v>
       </c>
       <c r="R11">
         <v>85.40000000000001</v>
@@ -3201,7 +3156,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>97.90000000000001</v>
@@ -3260,7 +3215,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R13">
         <v>93.8</v>
@@ -3319,7 +3274,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R14">
         <v>96.90000000000001</v>
@@ -3378,7 +3333,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3437,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3496,7 +3451,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>60.4</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
         <v>95.8</v>
@@ -3555,7 +3510,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R18">
         <v>95.8</v>
@@ -3614,7 +3569,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>99</v>
@@ -3673,7 +3628,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R20">
         <v>96.90000000000001</v>
@@ -3732,7 +3687,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3791,7 +3746,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R22">
         <v>95.8</v>
@@ -3850,7 +3805,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>54.2</v>
+        <v>87.5</v>
       </c>
       <c r="R23">
         <v>90.59999999999999</v>
@@ -3864,13 +3819,13 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -3879,16 +3834,16 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -3897,16 +3852,16 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -3915,7 +3870,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -3968,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4027,7 +3982,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>97.90000000000001</v>
@@ -4086,7 +4041,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>96.90000000000001</v>
@@ -4158,19 +4113,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4190,25 +4145,25 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4222,13 +4177,13 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
@@ -4237,10 +4192,10 @@
         <v>8.5</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4254,13 +4209,13 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
@@ -4269,10 +4224,10 @@
         <v>8.9</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4286,13 +4241,13 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -4301,10 +4256,10 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4346,7 +4301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4373,86 +4328,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920225</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920225</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4460,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4490,190 +4365,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920225</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920225</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920225</v>
-      </c>
-      <c r="B5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920394</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920374</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920222</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
